--- a/Config/Datas/TileDatas/TileData.xlsx
+++ b/Config/Datas/TileDatas/TileData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityProject\BBQ\Config\Datas\TileDatas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16BAA5E4-ED96-4D1D-AC76-C679FB49B709}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{05D0115D-C887-4C06-B0BD-426E91BA9532}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="24">
   <si>
     <t>##var</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -48,6 +48,78 @@
   </si>
   <si>
     <t>string</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Default</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>默认</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>默认的地块</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Ice</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>冰</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>冰面，会滑</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>*CGAs</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>list,CardCGA</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>type</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>action</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>*conditions</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>*actions</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>list,Condition</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>list,GameAction</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>滑动</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>DV_值,1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>实体移动进入</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>GA_滑行</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -55,7 +127,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -73,6 +145,14 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
       <name val="等线"/>
       <family val="3"/>
       <charset val="134"/>
@@ -99,10 +179,25 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -384,13 +479,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D2"/>
+  <dimension ref="A1:N7"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="4" max="4" width="10.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -403,8 +498,20 @@
       <c r="D1" s="1" t="s">
         <v>4</v>
       </c>
+      <c r="E1" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F1" s="2"/>
+      <c r="G1" s="2"/>
+      <c r="H1" s="2"/>
+      <c r="I1" s="2"/>
+      <c r="J1" s="2"/>
+      <c r="K1" s="2"/>
+      <c r="L1" s="2"/>
+      <c r="M1" s="2"/>
+      <c r="N1" s="2"/>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -417,8 +524,124 @@
       <c r="D2" s="1" t="s">
         <v>5</v>
       </c>
+      <c r="E2" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="F2" s="3"/>
+      <c r="G2" s="3"/>
+      <c r="H2" s="3"/>
+      <c r="I2" s="3"/>
+      <c r="J2" s="3"/>
+      <c r="K2" s="3"/>
+      <c r="L2" s="3"/>
+      <c r="M2" s="3"/>
+      <c r="N2" s="3"/>
+    </row>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>0</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="G3" s="3"/>
+      <c r="H3" s="3"/>
+      <c r="I3" s="3"/>
+      <c r="J3" s="3"/>
+      <c r="K3" s="3"/>
+      <c r="L3" s="3"/>
+      <c r="M3" s="3"/>
+      <c r="N3" s="3"/>
+    </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>0</v>
+      </c>
+      <c r="E4" s="4"/>
+      <c r="F4" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H4" s="3"/>
+      <c r="I4" s="3"/>
+      <c r="J4" s="3"/>
+      <c r="K4" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="L4" s="6"/>
+      <c r="M4" s="6"/>
+      <c r="N4" s="6"/>
+    </row>
+    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>1</v>
+      </c>
+      <c r="E5" s="4"/>
+      <c r="F5" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="H5" s="3"/>
+      <c r="I5" s="3"/>
+      <c r="J5" s="3"/>
+      <c r="K5" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="L5" s="6"/>
+      <c r="M5" s="6"/>
+      <c r="N5" s="6"/>
+    </row>
+    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="B6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C6" t="s">
+        <v>7</v>
+      </c>
+      <c r="D6" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="B7" t="s">
+        <v>9</v>
+      </c>
+      <c r="C7" t="s">
+        <v>10</v>
+      </c>
+      <c r="D7" t="s">
+        <v>11</v>
+      </c>
+      <c r="E7" t="s">
+        <v>22</v>
+      </c>
+      <c r="F7" t="s">
+        <v>20</v>
+      </c>
+      <c r="K7" t="s">
+        <v>23</v>
+      </c>
+      <c r="L7" t="s">
+        <v>21</v>
+      </c>
     </row>
   </sheetData>
+  <mergeCells count="7">
+    <mergeCell ref="E1:N1"/>
+    <mergeCell ref="E2:N2"/>
+    <mergeCell ref="F3:N3"/>
+    <mergeCell ref="G4:J4"/>
+    <mergeCell ref="K4:N4"/>
+    <mergeCell ref="G5:J5"/>
+    <mergeCell ref="K5:N5"/>
+  </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Config/Datas/TileDatas/TileData.xlsx
+++ b/Config/Datas/TileDatas/TileData.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29628"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityProject\BBQ\Config\Datas\TileDatas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{05D0115D-C887-4C06-B0BD-426E91BA9532}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F7F87D8-27B6-403A-9FAD-6904FA5E70B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="26">
   <si>
     <t>##var</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -120,6 +120,14 @@
   </si>
   <si>
     <t>GA_滑行</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>spriteName</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>AI地块_0</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -184,9 +192,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -198,6 +203,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -479,13 +487,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:N7"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:O9"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="4" max="4" width="10.5" customWidth="1"/>
+    <col min="4" max="5" width="10.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -498,20 +506,23 @@
       <c r="D1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="F1" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="F1" s="2"/>
-      <c r="G1" s="2"/>
-      <c r="H1" s="2"/>
-      <c r="I1" s="2"/>
-      <c r="J1" s="2"/>
-      <c r="K1" s="2"/>
-      <c r="L1" s="2"/>
-      <c r="M1" s="2"/>
-      <c r="N1" s="2"/>
-    </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="G1" s="6"/>
+      <c r="H1" s="6"/>
+      <c r="I1" s="6"/>
+      <c r="J1" s="6"/>
+      <c r="K1" s="6"/>
+      <c r="L1" s="6"/>
+      <c r="M1" s="6"/>
+      <c r="N1" s="6"/>
+      <c r="O1" s="6"/>
+    </row>
+    <row r="2" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -524,81 +535,84 @@
       <c r="D2" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="E2" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="F2" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="F2" s="3"/>
-      <c r="G2" s="3"/>
-      <c r="H2" s="3"/>
-      <c r="I2" s="3"/>
-      <c r="J2" s="3"/>
-      <c r="K2" s="3"/>
-      <c r="L2" s="3"/>
-      <c r="M2" s="3"/>
-      <c r="N2" s="3"/>
-    </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="G2" s="4"/>
+      <c r="H2" s="4"/>
+      <c r="I2" s="4"/>
+      <c r="J2" s="4"/>
+      <c r="K2" s="4"/>
+      <c r="L2" s="4"/>
+      <c r="M2" s="4"/>
+      <c r="N2" s="4"/>
+      <c r="O2" s="4"/>
+    </row>
+    <row r="3" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>0</v>
       </c>
-      <c r="E3" s="4" t="s">
+      <c r="F3" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="F3" s="3" t="s">
+      <c r="G3" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="G3" s="3"/>
-      <c r="H3" s="3"/>
-      <c r="I3" s="3"/>
-      <c r="J3" s="3"/>
-      <c r="K3" s="3"/>
-      <c r="L3" s="3"/>
-      <c r="M3" s="3"/>
-      <c r="N3" s="3"/>
-    </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="H3" s="4"/>
+      <c r="I3" s="4"/>
+      <c r="J3" s="4"/>
+      <c r="K3" s="4"/>
+      <c r="L3" s="4"/>
+      <c r="M3" s="4"/>
+      <c r="N3" s="4"/>
+      <c r="O3" s="4"/>
+    </row>
+    <row r="4" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>0</v>
       </c>
-      <c r="E4" s="4"/>
-      <c r="F4" s="5" t="s">
+      <c r="F4" s="3"/>
+      <c r="G4" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="G4" s="3" t="s">
+      <c r="H4" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="H4" s="3"/>
-      <c r="I4" s="3"/>
-      <c r="J4" s="3"/>
-      <c r="K4" s="6" t="s">
+      <c r="I4" s="4"/>
+      <c r="J4" s="4"/>
+      <c r="K4" s="4"/>
+      <c r="L4" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="L4" s="6"/>
-      <c r="M4" s="6"/>
-      <c r="N4" s="6"/>
-    </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="M4" s="5"/>
+      <c r="N4" s="5"/>
+      <c r="O4" s="5"/>
+    </row>
+    <row r="5" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>1</v>
       </c>
-      <c r="E5" s="4"/>
-      <c r="F5" s="5" t="s">
+      <c r="F5" s="3"/>
+      <c r="G5" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G5" s="3" t="s">
+      <c r="H5" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="H5" s="3"/>
-      <c r="I5" s="3"/>
-      <c r="J5" s="3"/>
-      <c r="K5" s="6" t="s">
+      <c r="I5" s="4"/>
+      <c r="J5" s="4"/>
+      <c r="K5" s="4"/>
+      <c r="L5" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="L5" s="6"/>
-      <c r="M5" s="6"/>
-      <c r="N5" s="6"/>
-    </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="M5" s="5"/>
+      <c r="N5" s="5"/>
+      <c r="O5" s="5"/>
+    </row>
+    <row r="6" spans="1:15" x14ac:dyDescent="0.3">
       <c r="B6" t="s">
         <v>6</v>
       </c>
@@ -609,7 +623,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.3">
       <c r="B7" t="s">
         <v>9</v>
       </c>
@@ -620,27 +634,33 @@
         <v>11</v>
       </c>
       <c r="E7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F7" t="s">
         <v>22</v>
       </c>
-      <c r="F7" t="s">
+      <c r="G7" t="s">
         <v>20</v>
       </c>
-      <c r="K7" t="s">
+      <c r="L7" t="s">
         <v>23</v>
       </c>
-      <c r="L7" t="s">
+      <c r="M7" t="s">
         <v>21</v>
       </c>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="E9" s="1"/>
     </row>
   </sheetData>
   <mergeCells count="7">
-    <mergeCell ref="E1:N1"/>
-    <mergeCell ref="E2:N2"/>
-    <mergeCell ref="F3:N3"/>
-    <mergeCell ref="G4:J4"/>
-    <mergeCell ref="K4:N4"/>
-    <mergeCell ref="G5:J5"/>
-    <mergeCell ref="K5:N5"/>
+    <mergeCell ref="H5:K5"/>
+    <mergeCell ref="L5:O5"/>
+    <mergeCell ref="F1:O1"/>
+    <mergeCell ref="F2:O2"/>
+    <mergeCell ref="G3:O3"/>
+    <mergeCell ref="H4:K4"/>
+    <mergeCell ref="L4:O4"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
